--- a/002_backLinks/Free Backlinks List.xlsx
+++ b/002_backLinks/Free Backlinks List.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18825" windowHeight="7920"/>
+    <workbookView windowWidth="13800" windowHeight="7830"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="30">
   <si>
     <t>No.</t>
   </si>
@@ -69,9 +69,6 @@
   </si>
   <si>
     <t>post</t>
-  </si>
-  <si>
-    <t>https://bots.ondiscord.xyz</t>
   </si>
   <si>
     <t>https://meta.appinn.net</t>
@@ -756,7 +753,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -776,9 +773,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="6" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1318,7 +1312,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultColWidth="9.06666666666667" defaultRowHeight="16.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="9.06666666666667" style="1"/>
@@ -1372,7 +1366,7 @@
     </row>
     <row r="4" s="1" customFormat="1" spans="1:4">
       <c r="A4" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="3">
         <v>56</v>
@@ -1386,7 +1380,7 @@
     </row>
     <row r="5" s="1" customFormat="1" spans="1:4">
       <c r="A5" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" s="3">
         <v>28</v>
@@ -1400,7 +1394,7 @@
     </row>
     <row r="6" s="1" customFormat="1" spans="1:4">
       <c r="A6" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" s="3">
         <v>60</v>
@@ -1414,7 +1408,7 @@
     </row>
     <row r="7" s="1" customFormat="1" spans="1:4">
       <c r="A7" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>10</v>
@@ -1428,10 +1422,10 @@
     </row>
     <row r="8" s="1" customFormat="1" spans="1:4">
       <c r="A8" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="3">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>13</v>
@@ -1442,38 +1436,38 @@
     </row>
     <row r="9" s="1" customFormat="1" spans="1:4">
       <c r="A9" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" s="3">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="7" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" spans="1:4">
       <c r="A10" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B10" s="3">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" spans="1:4">
       <c r="A11" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="3">
-        <v>78</v>
+        <v>19</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>13</v>
@@ -1484,108 +1478,108 @@
     </row>
     <row r="12" s="1" customFormat="1" spans="1:4">
       <c r="A12" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="3">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" s="6" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" spans="1:4">
       <c r="A13" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="3">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="7" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" spans="1:4">
       <c r="A14" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14" s="3">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" spans="1:4">
+    <row r="15" spans="1:4">
       <c r="A15" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" s="3">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="3">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B16" s="3">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="D16" s="7" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B17" s="3">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="D17" s="7" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" s="3">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="7" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B19" s="3">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>4</v>
@@ -1596,56 +1590,42 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20" s="3">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D20" s="9" t="s">
+      <c r="D20" s="7" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B21" s="3">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="7" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="3">
-        <v>22</v>
-      </c>
-      <c r="B22" s="3">
-        <v>56</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D22" s="8" t="s">
+    <row r="24" spans="1:2">
+      <c r="A24" s="9" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="10" t="s">
+      <c r="B24" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
-      <c r="A26" s="11"/>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="10"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1655,21 +1635,20 @@
     <hyperlink ref="D5" r:id="rId4" display="https://tinyhunt.dev/" tooltip="https://tinyhunt.dev/"/>
     <hyperlink ref="D6" r:id="rId5" display="https://websitelaunches.com/" tooltip="https://websitelaunches.com/"/>
     <hyperlink ref="D7" r:id="rId6" display="https://dev.to/" tooltip="https://dev.to/"/>
-    <hyperlink ref="D8" r:id="rId7" display="https://bots.ondiscord.xyz" tooltip="https://bots.ondiscord.xyz"/>
-    <hyperlink ref="D9" r:id="rId8" display="https://meta.appinn.net" tooltip="https://meta.appinn.net"/>
-    <hyperlink ref="D11" r:id="rId9" display="https://www.v2ex.com/" tooltip="https://www.v2ex.com/"/>
-    <hyperlink ref="D12" r:id="rId10" display="https://launch01.com/" tooltip="https://launch01.com/"/>
-    <hyperlink ref="D13" r:id="rId11" display="https://aiproducthub.cn/" tooltip="https://aiproducthub.cn/"/>
-    <hyperlink ref="D15" r:id="rId12" display="https://futuretools.io/" tooltip="https://futuretools.io/"/>
-    <hyperlink ref="D16" r:id="rId13" display="https://aitoolsdirectory.com/" tooltip="https://aitoolsdirectory.com/"/>
-    <hyperlink ref="D17" r:id="rId14" display="https://startupbase.io/" tooltip="https://startupbase.io/"/>
-    <hyperlink ref="D18" r:id="rId15" display="https://aitoptools.com/" tooltip="https://aitoptools.com/"/>
-    <hyperlink ref="D19" r:id="rId16" display="https://www.launchingnext.com/" tooltip="https://www.launchingnext.com/"/>
-    <hyperlink ref="D20" r:id="rId17" display="https://www.startupranking.com" tooltip="https://www.startupranking.com"/>
-    <hyperlink ref="D21" r:id="rId18" display="https://fazier.com/l" tooltip="https://fazier.com/l"/>
-    <hyperlink ref="D22" r:id="rId19" display="https://www.ainav.cn/" tooltip="https://www.ainav.cn/"/>
-    <hyperlink ref="D10" r:id="rId20" display="https://news.ycombinator.com" tooltip="https://news.ycombinator.com"/>
-    <hyperlink ref="D14" r:id="rId21" display="https://www.meoai.net/" tooltip="https://www.meoai.net/"/>
+    <hyperlink ref="D8" r:id="rId7" display="https://meta.appinn.net" tooltip="https://meta.appinn.net"/>
+    <hyperlink ref="D10" r:id="rId8" display="https://www.v2ex.com/" tooltip="https://www.v2ex.com/"/>
+    <hyperlink ref="D11" r:id="rId9" display="https://launch01.com/" tooltip="https://launch01.com/"/>
+    <hyperlink ref="D12" r:id="rId10" display="https://aiproducthub.cn/" tooltip="https://aiproducthub.cn/"/>
+    <hyperlink ref="D14" r:id="rId11" display="https://futuretools.io/" tooltip="https://futuretools.io/"/>
+    <hyperlink ref="D15" r:id="rId12" display="https://aitoolsdirectory.com/" tooltip="https://aitoolsdirectory.com/"/>
+    <hyperlink ref="D16" r:id="rId13" display="https://startupbase.io/" tooltip="https://startupbase.io/"/>
+    <hyperlink ref="D17" r:id="rId14" display="https://aitoptools.com/" tooltip="https://aitoptools.com/"/>
+    <hyperlink ref="D18" r:id="rId15" display="https://www.launchingnext.com/" tooltip="https://www.launchingnext.com/"/>
+    <hyperlink ref="D19" r:id="rId16" display="https://www.startupranking.com" tooltip="https://www.startupranking.com"/>
+    <hyperlink ref="D20" r:id="rId17" display="https://fazier.com/l" tooltip="https://fazier.com/l"/>
+    <hyperlink ref="D21" r:id="rId18" display="https://www.ainav.cn/" tooltip="https://www.ainav.cn/"/>
+    <hyperlink ref="D9" r:id="rId19" display="https://news.ycombinator.com" tooltip="https://news.ycombinator.com"/>
+    <hyperlink ref="D13" r:id="rId20" display="https://www.meoai.net/" tooltip="https://www.meoai.net/"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
